--- a/data/trans_dic/P37A$medicoenfermedad-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicoenfermedad-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,46</t>
+          <t>1,3; 4,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,85</t>
+          <t>0,71; 4,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,77</t>
+          <t>1,61; 4,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,61</t>
+          <t>3,72; 7,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,66</t>
+          <t>0,26; 2,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,65</t>
+          <t>1,87; 6,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,07</t>
+          <t>0,86; 4,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,76</t>
+          <t>3,35; 6,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,22</t>
+          <t>1,07; 3,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,07</t>
+          <t>1,53; 4,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,92</t>
+          <t>1,52; 3,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,08</t>
+          <t>3,98; 6,35</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,82</t>
+          <t>1,25; 4,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,38</t>
+          <t>0,76; 4,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,48</t>
+          <t>1,02; 4,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,93</t>
+          <t>3,13; 6,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,03</t>
+          <t>0,53; 3,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,58</t>
+          <t>0,79; 4,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,7</t>
+          <t>1,77; 5,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 10,59</t>
+          <t>5,85; 10,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,23</t>
+          <t>1,16; 3,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,52</t>
+          <t>1,05; 3,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,43</t>
+          <t>1,75; 4,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,9</t>
+          <t>4,78; 7,79</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -997,37 +997,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,91</t>
+          <t>1,66; 4,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 8,18</t>
+          <t>3,85; 7,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,9</t>
+          <t>3,15; 6,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,56</t>
+          <t>3,47; 7,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,4</t>
+          <t>1,1; 6,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,6</t>
+          <t>0,75; 4,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,36</t>
+          <t>0,63; 6,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,77</t>
+          <t>1,84; 4,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,57</t>
+          <t>3,46; 6,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,05</t>
+          <t>2,82; 6,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,54</t>
+          <t>4,41; 7,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 6,05</t>
+          <t>3,68; 6,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 5,53</t>
+          <t>3,16; 5,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,71</t>
+          <t>3,2; 5,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,07</t>
+          <t>5,63; 8,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,43</t>
+          <t>2,69; 5,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,16</t>
+          <t>2,28; 4,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,54</t>
+          <t>1,39; 3,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,86</t>
+          <t>2,7; 4,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,5</t>
+          <t>3,62; 5,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,93</t>
+          <t>3,16; 4,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,35</t>
+          <t>2,69; 4,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,1</t>
+          <t>4,7; 6,59</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,02</t>
+          <t>1,71; 5,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,31</t>
+          <t>1,43; 4,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,19</t>
+          <t>1,67; 4,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,54</t>
+          <t>4,12; 7,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,75</t>
+          <t>1,92; 4,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,03</t>
+          <t>2,45; 5,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,62</t>
+          <t>2,65; 5,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,55</t>
+          <t>5,44; 8,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,48</t>
+          <t>2,14; 4,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,19</t>
+          <t>2,29; 4,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,49</t>
+          <t>2,5; 4,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,24</t>
+          <t>5,3; 7,71</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,47</t>
+          <t>0,62; 3,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,87</t>
+          <t>1,43; 5,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,66</t>
+          <t>0,72; 4,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,33</t>
+          <t>0,29; 3,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,94</t>
+          <t>2,01; 3,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,27</t>
+          <t>4,43; 7,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,41</t>
+          <t>2,03; 4,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,79; 10,85</t>
+          <t>7,7; 10,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,57</t>
+          <t>1,9; 3,54</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,47</t>
+          <t>4,02; 6,62</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,94</t>
+          <t>1,94; 3,98</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,65</t>
+          <t>6,23; 8,81</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,12</t>
+          <t>2,85; 4,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,04; 4,38</t>
+          <t>2,96; 4,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 4,14</t>
+          <t>2,83; 4,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,12</t>
+          <t>4,92; 6,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,34</t>
+          <t>2,25; 3,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 4,74</t>
+          <t>3,34; 4,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 3,62</t>
+          <t>2,44; 3,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,57</t>
+          <t>5,74; 7,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,53</t>
+          <t>2,72; 3,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,36</t>
+          <t>3,36; 4,29</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,66</t>
+          <t>2,82; 3,67</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,12</t>
+          <t>5,57; 6,58</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23807</t>
+          <t>28981</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>23496</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44899</t>
+          <t>52477</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6497; 21129</t>
+          <t>6154; 21832</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3162; 16850</t>
+          <t>3109; 17933</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6420; 20457</t>
+          <t>6901; 21349</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16391; 33376</t>
+          <t>20478; 41412</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>800; 8144</t>
+          <t>808; 8651</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5581; 20900</t>
+          <t>5895; 19454</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3101; 14114</t>
+          <t>2986; 15559</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14621; 30255</t>
+          <t>16382; 32447</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8599; 25156</t>
+          <t>8387; 23881</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11398; 30590</t>
+          <t>11474; 30052</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11952; 30418</t>
+          <t>11832; 29775</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35141; 57888</t>
+          <t>41344; 65949</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21712</t>
+          <t>23208</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29747</t>
+          <t>32610</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51460</t>
+          <t>55818</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4502; 17698</t>
+          <t>4598; 17203</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4113; 18337</t>
+          <t>3168; 17240</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3803; 16905</t>
+          <t>3833; 16189</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14965; 31346</t>
+          <t>15136; 33520</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1962; 11278</t>
+          <t>1980; 11495</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1955; 15465</t>
+          <t>2673; 15296</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6108; 21207</t>
+          <t>6577; 21091</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22517; 40498</t>
+          <t>24762; 43464</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8611; 23880</t>
+          <t>8587; 24938</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7947; 26677</t>
+          <t>7938; 26035</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13045; 33195</t>
+          <t>13091; 32666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40825; 65977</t>
+          <t>43279; 70599</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24604</t>
+          <t>25746</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36180</t>
+          <t>38210</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8481; 26644</t>
+          <t>8999; 26478</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24982; 51481</t>
+          <t>24227; 49479</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16432; 36027</t>
+          <t>16456; 36351</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8232; 43849</t>
+          <t>16351; 35292</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1969; 12416</t>
+          <t>1838; 11252</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2075; 11955</t>
+          <t>1961; 11923</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1047; 10568</t>
+          <t>1040; 11381</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7323; 17317</t>
+          <t>8236; 19451</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13984; 33888</t>
+          <t>13067; 33999</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30820; 58464</t>
+          <t>30742; 58326</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18765; 41611</t>
+          <t>19399; 41992</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15212; 54637</t>
+          <t>29053; 49541</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74047</t>
+          <t>79630</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26474</t>
+          <t>30832</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>100521</t>
+          <t>110462</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46288; 74896</t>
+          <t>45573; 74381</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36056; 64102</t>
+          <t>36587; 64528</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36831; 65662</t>
+          <t>36739; 65232</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59238; 93878</t>
+          <t>63675; 100594</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17701; 38812</t>
+          <t>19189; 37547</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17392; 39558</t>
+          <t>17517; 38016</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11338; 29203</t>
+          <t>11443; 28580</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13818; 37787</t>
+          <t>23223; 40404</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70821; 107421</t>
+          <t>70611; 106123</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60137; 94945</t>
+          <t>60883; 94061</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53842; 85871</t>
+          <t>53184; 86966</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69693; 122692</t>
+          <t>93642; 131351</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>32635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48728</t>
+          <t>55986</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78699</t>
+          <t>88621</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5616; 17601</t>
+          <t>5994; 18546</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7829; 21994</t>
+          <t>7310; 22471</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9806; 26005</t>
+          <t>10391; 27669</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22123; 40566</t>
+          <t>23421; 43607</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10740; 27023</t>
+          <t>10913; 27916</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17434; 38311</t>
+          <t>18651; 39897</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19606; 41505</t>
+          <t>19534; 40999</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34871; 63501</t>
+          <t>45221; 69851</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19412; 41201</t>
+          <t>19714; 42316</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28879; 53303</t>
+          <t>29116; 53863</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34118; 61020</t>
+          <t>33995; 60705</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61172; 95301</t>
+          <t>74190; 107872</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>69968</t>
+          <t>77404</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>72948</t>
+          <t>80310</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1859; 10362</t>
+          <t>1856; 10667</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3159; 15667</t>
+          <t>3811; 15773</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2035; 13373</t>
+          <t>2058; 13970</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>912; 8004</t>
+          <t>696; 7559</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26677; 49201</t>
+          <t>25139; 49164</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48721; 80616</t>
+          <t>49105; 81359</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22946; 47700</t>
+          <t>21915; 47000</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>59301; 82625</t>
+          <t>65030; 90540</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30311; 55257</t>
+          <t>29351; 54702</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56502; 89079</t>
+          <t>55317; 91125</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27850; 53938</t>
+          <t>26503; 54429</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>61320; 86647</t>
+          <t>67425; 95243</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177122</t>
+          <t>193108</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>207584</t>
+          <t>232791</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>384706</t>
+          <t>425899</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>94641; 134826</t>
+          <t>93200; 135831</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>104012; 149929</t>
+          <t>101441; 147356</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>96755; 140143</t>
+          <t>95880; 140714</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>138618; 206542</t>
+          <t>169534; 219528</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>75466; 112784</t>
+          <t>76013; 114496</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>120414; 168393</t>
+          <t>118580; 166278</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85285; 127983</t>
+          <t>86105; 128694</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>169834; 235063</t>
+          <t>208818; 257201</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>178702; 234874</t>
+          <t>180921; 238399</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>237037; 303710</t>
+          <t>234282; 298788</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>191675; 252887</t>
+          <t>195334; 254091</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>329708; 425509</t>
+          <t>394009; 465824</t>
         </is>
       </c>
     </row>
